--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/12_Segundo_Turno_Lula_vs_Renan_por_Religiao.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/12_Segundo_Turno_Lula_vs_Renan_por_Religiao.xlsx
@@ -23,7 +23,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Linhas_publicadas" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suavizados_Catolicos'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IC_Baixo_Catolicos'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IC_Alto_Catolicos'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Suavizados_Evangelicos'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'IC_Baixo_Evangelicos'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'IC_Alto_Evangelicos'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Suavizados_Outras_Religioes'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'IC_Baixo_Outras_Religioes'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'IC_Alto_Outras_Religioes'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Suavizados_Sem_Religiao'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'IC_Baixo_Sem_Religiao'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'IC_Alto_Sem_Religiao'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cobertura'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Metodologia'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Linhas_publicadas'!$A$1:$X$17</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -34,7 +50,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,16 +61,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -68,17 +93,35 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,54 +487,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>65.89524969549331</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>34.1047503045067</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>64.25506495775859</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>35.74493504224141</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>63.89659487073514</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>36.10340512926484</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>62.79017272143773</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>37.20982727856227</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -502,54 +568,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>62.87878787878789</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>37.12121212121212</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>64.3303560288544</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>35.6696439711456</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>64.60339434752859</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>35.39660565247141</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>66.01953162980669</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>33.98046837019329</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -560,54 +649,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>57.4117684328896</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>31.65419267531383</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>60.45528840284075</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>31.79457634513196</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>61.45889370537676</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>32.25210501031957</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>62.82165789726958</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>30.78259463765617</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,54 +730,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>68.34580732468618</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>42.58823156711041</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>68.20542365486804</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>39.54471159715925</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>67.74789498968043</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>38.54110629462324</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>69.2174053623438</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>37.1783421027304</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -676,33 +811,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>observacoes_publicadas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>primeira_data</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>ultima_data</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>numero_institutos</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>institutos</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>amostras_segmento_publicadas</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>fallbacks_amostra_segmento</t>
         </is>
       </c>
     </row>
@@ -715,16 +875,25 @@
       <c r="B2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="7" t="n">
         <v>46185</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -736,16 +905,25 @@
       <c r="B3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="7" t="n">
         <v>46185</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -757,16 +935,25 @@
       <c r="B4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="7" t="n">
         <v>46185</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -778,19 +965,29 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="7" t="n">
         <v>46185</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -801,16 +998,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
@@ -822,7 +1023,7 @@
           <t>Universo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Brasil, 2º turno, estimulada, Lula × Renan Santos.</t>
         </is>
@@ -834,9 +1035,9 @@
           <t>Abertura</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Grupos publicados de religião; rótulos equivalentes são harmonizados conforme a aba Metodologia.</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Grupos publicados de religião; somente rótulos equivalentes são harmonizados.</t>
         </is>
       </c>
     </row>
@@ -846,7 +1047,7 @@
           <t>Medida</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Lula e adversário convertidos para votos válidos dentro de cada grupo.</t>
         </is>
@@ -855,28 +1056,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amostra e IC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Usa amostra do segmento quando publicada; na ausência, o código aplica fallback conservador e isso não equivale à margem de erro total da pesquisa.</t>
+          <t>Cobertura mínima</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Exige ao menos dois grupos e duas datas publicadas em cada grupo desenhado.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Amostra e faixa</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Usa amostra do segmento quando publicada; na ausência, aplica fallback conservador. A faixa é apenas amostral e aproximada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Interpretação</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral.</t>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral nem probabilidade de vitória.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -887,128 +1101,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>instituto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>tipo_pesquisa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>frequencia_original</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>amostra_total</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>margem_erro_pp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>nivel_confianca_pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>turno</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>tipo_cenario</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>cenario</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>adversario</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>nivel_geografico</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>geografia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>segmento_tipo</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>amostra_segmento</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>lula_pct</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>adversario_pct</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>outros_candidatos_pct</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>brancos_nulos_indecisos_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>base_voto</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>_linha_excel</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>peso_legacy</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>grupo_abertura</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1029,7 +1274,7 @@
       <c r="E2" t="n">
         <v>2000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
@@ -1075,7 +1320,7 @@
           <t>Católica</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="6" t="n">
         <v>54.1</v>
       </c>
       <c r="R2" t="n">
@@ -1084,7 +1329,7 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="6" t="n">
         <v>17.8</v>
       </c>
       <c r="U2" t="inlineStr">
@@ -1093,16 +1338,19 @@
         </is>
       </c>
       <c r="V2" t="n">
+        <v>1387</v>
+      </c>
+      <c r="W2" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1123,7 +1371,7 @@
       <c r="E3" t="n">
         <v>2000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G3" t="n">
@@ -1169,10 +1417,10 @@
           <t>Evangélica</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="6" t="n">
         <v>34.1</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="6" t="n">
         <v>36.9</v>
       </c>
       <c r="S3" t="n">
@@ -1187,16 +1435,19 @@
         </is>
       </c>
       <c r="V3" t="n">
+        <v>1388</v>
+      </c>
+      <c r="W3" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1217,7 +1468,7 @@
       <c r="E4" t="n">
         <v>2000</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G4" t="n">
@@ -1263,16 +1514,16 @@
           <t>Outras Religiões</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="6" t="n">
         <v>44.1</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="6" t="n">
         <v>37.3</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="6" t="n">
         <v>18.5</v>
       </c>
       <c r="U4" t="inlineStr">
@@ -1281,16 +1532,19 @@
         </is>
       </c>
       <c r="V4" t="n">
+        <v>1391</v>
+      </c>
+      <c r="W4" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1311,7 +1565,7 @@
       <c r="E5" t="n">
         <v>2000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G5" t="n">
@@ -1357,16 +1611,16 @@
           <t>Nenhuma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="6" t="n">
         <v>49.8</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="6" t="n">
         <v>29.4</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="6" t="n">
         <v>20.7</v>
       </c>
       <c r="U5" t="inlineStr">
@@ -1375,16 +1629,19 @@
         </is>
       </c>
       <c r="V5" t="n">
+        <v>1390</v>
+      </c>
+      <c r="W5" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1469,16 +1726,19 @@
         </is>
       </c>
       <c r="V6" t="n">
+        <v>1563</v>
+      </c>
+      <c r="W6" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1563,16 +1823,19 @@
         </is>
       </c>
       <c r="V7" t="n">
+        <v>1564</v>
+      </c>
+      <c r="W7" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1657,16 +1920,19 @@
         </is>
       </c>
       <c r="V8" t="n">
+        <v>1565</v>
+      </c>
+      <c r="W8" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1751,16 +2017,19 @@
         </is>
       </c>
       <c r="V9" t="n">
+        <v>1566</v>
+      </c>
+      <c r="W9" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1845,16 +2114,19 @@
         </is>
       </c>
       <c r="V10" t="n">
+        <v>1796</v>
+      </c>
+      <c r="W10" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1939,16 +2211,19 @@
         </is>
       </c>
       <c r="V11" t="n">
+        <v>1797</v>
+      </c>
+      <c r="W11" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -2033,16 +2308,19 @@
         </is>
       </c>
       <c r="V12" t="n">
+        <v>1798</v>
+      </c>
+      <c r="W12" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2127,16 +2405,19 @@
         </is>
       </c>
       <c r="V13" t="n">
+        <v>1799</v>
+      </c>
+      <c r="W13" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2221,16 +2502,19 @@
         </is>
       </c>
       <c r="V14" t="n">
+        <v>2012</v>
+      </c>
+      <c r="W14" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Católicos</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2315,16 +2599,19 @@
         </is>
       </c>
       <c r="V15" t="n">
+        <v>2013</v>
+      </c>
+      <c r="W15" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Evangélicos</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2409,16 +2696,19 @@
         </is>
       </c>
       <c r="V16" t="n">
+        <v>2014</v>
+      </c>
+      <c r="W16" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Outras religiões</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2503,15 +2793,19 @@
         </is>
       </c>
       <c r="V17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="W17" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Sem religião</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2522,54 +2816,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>60.53083980245924</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>28.74034041147264</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>60.39072810724027</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>31.88059819172309</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>60.74484060505615</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>32.95165086358585</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>59.52692425200664</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>33.94657880913118</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2580,54 +2897,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>71.25965958852737</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>39.46916019754077</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>68.1194018082769</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>39.60927189275973</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>67.04834913641413</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>39.25515939494383</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>66.05342119086882</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>40.47307574799336</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2638,54 +2978,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>48.02816901408451</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>51.97183098591549</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>45.73686386198347</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>54.26313613801652</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>44.69094809544646</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>55.30905190455353</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>44.71583998536526</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>55.28416001463474</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2696,54 +3059,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>42.37464179392924</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>46.31830376576021</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>41.71322440591349</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>50.23949668194655</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>41.42631860736321</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>52.04442241647028</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>41.35922119244074</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>51.92754122171021</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2754,54 +3140,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>53.68169623423979</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>57.62535820607076</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>49.76050331805344</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>58.28677559408649</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>47.95557758352971</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>58.57368139263679</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>48.07245877828979</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>58.64077880755926</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2812,54 +3221,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>54.17690417690417</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>45.82309582309582</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>58.05265090200773</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>41.94734909799227</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>56.3822779311318</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>43.6177220688682</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>55.20706325163355</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>44.79293674836644</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2870,54 +3302,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>48.5387523133568</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>40.18494395954845</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>54.0717136390651</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>37.96641183504964</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>53.13115163325049</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>40.36659577098689</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>51.8509448682812</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>41.4368183650141</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2928,54 +3383,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>59.81505604045155</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>51.46124768664319</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>62.03358816495035</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>45.92828636093489</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>59.6334042290131</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>46.8688483667495</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>58.5631816349859</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>48.14905513171879</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>